--- a/data/haver_names.xlsx
+++ b/data/haver_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malcalakovalski\Documents\fim\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahmad\Downloads\FIM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF3DC16-585A-427E-9D83-5EAFCF8B9A4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24227389-1697-4BE0-A19C-765689332D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6020" yWindow="1870" windowWidth="9600" windowHeight="4910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="152">
   <si>
     <t>code</t>
   </si>
@@ -466,6 +466,24 @@
   </si>
   <si>
     <t>social_security</t>
+  </si>
+  <si>
+    <t>gfrio</t>
+  </si>
+  <si>
+    <t>other_noncorp_taxes</t>
+  </si>
+  <si>
+    <t>gfrid</t>
+  </si>
+  <si>
+    <t>customs_duties</t>
+  </si>
+  <si>
+    <t>gfrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excise </t>
   </si>
 </sst>
 </file>
@@ -532,9 +550,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -572,9 +590,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -607,26 +625,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -659,26 +660,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -852,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
@@ -1450,6 +1434,30 @@
         <v>145</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" t="s">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -1457,21 +1465,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FA9F3DB0CD4D844B918872BCED9B9CF9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="61f75d9b13a46a58fd2456a565edcb9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cac5d118-ba7b-4807-b700-df6f95cfff50" xmlns:ns3="66951ee6-cd93-49c7-9437-e871b2a117d6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d86870d415110e2c98f3a885b29630d1" ns2:_="" ns3:_="">
     <xsd:import namespace="cac5d118-ba7b-4807-b700-df6f95cfff50"/>
@@ -1688,32 +1681,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11C50A7A-072C-42B0-A807-112C623C860C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C7CC3BF-DF9F-4E15-B3E2-3F2BE52E9D01}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="66951ee6-cd93-49c7-9437-e871b2a117d6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="cac5d118-ba7b-4807-b700-df6f95cfff50"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6FBE834-A7AF-4CA7-B4B3-E5BBA0B171E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1730,4 +1713,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11C50A7A-072C-42B0-A807-112C623C860C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C7CC3BF-DF9F-4E15-B3E2-3F2BE52E9D01}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="66951ee6-cd93-49c7-9437-e871b2a117d6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="cac5d118-ba7b-4807-b700-df6f95cfff50"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>